--- a/output/pdf_financials_xlsx/SATO.xlsx
+++ b/output/pdf_financials_xlsx/SATO.xlsx
@@ -4201,22 +4201,22 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.157894</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.000391</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.000174</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.283681</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.259268</v>
       </c>
     </row>
     <row r="92">
@@ -4232,13 +4232,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.056896</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.056896</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.056896</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.355354</v>
@@ -7505,7 +7505,11 @@
           <t>Digital currency revaluation reserve</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11086,7 +11090,11 @@
           <t>Digital currency revaluation reserve</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -14390,7 +14398,11 @@
           <t>Digital currency revaluation reserve -</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -15682,7 +15694,11 @@
           <t>Digital currency revaluation reserve</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -16443,7 +16459,11 @@
           <t>Share-based payments reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SATO.xlsx
+++ b/output/pdf_financials_xlsx/SATO.xlsx
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.008579</v>
+        <v>0.045851</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.002527</v>
+        <v>0.01812</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01056</v>
+        <v>0.115647</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.010687</v>
+        <v>0.024928</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.009334</v>
+        <v>0.03183</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.090556</v>
+        <v>0.043577</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.000961</v>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.008579</v>
+        <v>-0.045851</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.002527</v>
+        <v>-0.01812</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.01056</v>
+        <v>-0.115647</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.010687</v>
+        <v>-0.024928</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.009334</v>
+        <v>-0.03183</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.161447</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000638</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-1.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.063236</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.045213</v>
+        <v>-0.044575</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.018104</v>
+        <v>-0.018088</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.115497</v>
+        <v>-0.115647</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.024928</v>
@@ -1598,7 +1598,7 @@
         <v>0.776496</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.072368</v>
+        <v>1.135604</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.045213</v>
+        <v>-0.044575</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.018104</v>
+        <v>-0.018088</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.115497</v>
+        <v>-0.115647</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.024928</v>
@@ -1684,7 +1684,7 @@
         <v>3.316617</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.025425</v>
+        <v>4.088661</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>18.88663498675676</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>25.00695306264938</v>
+        <v>25.39979100743029</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -1867,28 +1867,28 @@
         <v>0.301152</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.239288</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.218749</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.294025</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000324</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000387</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.583151</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.658488</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.123677</v>
       </c>
     </row>
     <row r="35">
@@ -1947,28 +1947,28 @@
         <v>0.301152</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.239288</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.218749</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.294025</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000324</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000387</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.583151</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.658488</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.123677</v>
       </c>
     </row>
     <row r="37">
@@ -2433,22 +2433,22 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.011203</v>
+        <v>0.717178</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000719</v>
+        <v>0.000395</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.4e-05</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.088566</v>
+        <v>2.505415</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.386317</v>
+        <v>2.727829</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.391988</v>
+        <v>1.268311</v>
       </c>
     </row>
     <row r="49">
@@ -5498,10 +5498,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05598</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.104923</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -5538,10 +5538,10 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05598</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.104923</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -33097,7 +33097,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -38109,7 +38113,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -45060,7 +45064,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -45133,7 +45137,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -45147,19 +45151,19 @@
         </is>
       </c>
       <c r="G554" s="5" t="n">
-        <v>-0.115647</v>
+        <v>0.115647</v>
       </c>
       <c r="H554" s="5" t="n">
-        <v>-0.024928</v>
+        <v>0.024928</v>
       </c>
       <c r="I554" s="5" t="n">
-        <v>-0.03183</v>
+        <v>0.03183</v>
       </c>
       <c r="J554" s="5" t="n">
-        <v>-0.043577</v>
+        <v>0.043577</v>
       </c>
       <c r="K554" s="5" t="n">
-        <v>-0.036702</v>
+        <v>0.036702</v>
       </c>
       <c r="L554" t="inlineStr">
         <is>
@@ -46519,7 +46523,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -47075,7 +47079,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -47645,7 +47649,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E590" s="5" t="n">
@@ -47716,7 +47720,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" s="5" t="n">

--- a/output/pdf_financials_xlsx/SATO.xlsx
+++ b/output/pdf_financials_xlsx/SATO.xlsx
@@ -1104,7 +1104,7 @@
         <v>-5.2e-05</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.102279</v>
+        <v>-0.102279</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -3112,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.106963</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.132148</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.13089</v>
       </c>
     </row>
     <row r="65">
@@ -3232,13 +3232,13 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.944814</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.454643</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.449328</v>
       </c>
     </row>
     <row r="68">
@@ -19547,7 +19547,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -22448,7 +22452,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -35241,7 +35249,11 @@
           <t>Proceeds from private placement (Note 6)</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -38537,7 +38549,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
